--- a/TELEMETRYadcCLOCK/project/Summary.xlsx
+++ b/TELEMETRYadcCLOCK/project/Summary.xlsx
@@ -410,7 +410,7 @@
     <t>project_netlist_path</t>
   </si>
   <si>
-    <t>/tmp/kyle/mnt/celera/projects/Simplis/playcalum/Puget/Puget0/301A/overlay/SIMPLIS_Data/overlay_TELEMETRYadcCLOCK.net</t>
+    <t>/tmp/overlay_TELEMETRYadcCLOCK.net</t>
   </si>
   <si>
     <t>gen_reports</t>

--- a/TELEMETRYadcCLOCK/project/Summary.xlsx
+++ b/TELEMETRYadcCLOCK/project/Summary.xlsx
@@ -410,7 +410,7 @@
     <t>project_netlist_path</t>
   </si>
   <si>
-    <t>/tmp/overlay_TELEMETRYadcCLOCK.net</t>
+    <t>/tmp/kyle/mnt/celera/projects/Simplis/playcalum/Puget/Puget0/301A/overlay/SIMPLIS_Data/overlay_TELEMETRYadcCLOCK.net</t>
   </si>
   <si>
     <t>gen_reports</t>

--- a/TELEMETRYadcCLOCK/project/Summary.xlsx
+++ b/TELEMETRYadcCLOCK/project/Summary.xlsx
@@ -9,39 +9,38 @@
   <sheets>
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
-    <sheet name="Missing Bio Symbol Files" sheetId="3" r:id="rId3"/>
-    <sheet name="Missing Nets" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Inputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Shorted Outputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Inputs" sheetId="7" r:id="rId7"/>
-    <sheet name="Floating Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Outputs" sheetId="9" r:id="rId9"/>
-    <sheet name="No Connects - Inputs" sheetId="10" r:id="rId10"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="11" r:id="rId11"/>
-    <sheet name="Ring Core IO check report" sheetId="12" r:id="rId12"/>
-    <sheet name="D to A Tree" sheetId="13" r:id="rId13"/>
-    <sheet name="Symbol Length Exceed Max" sheetId="14" r:id="rId14"/>
-    <sheet name="Cell Length Exceed Max 50" sheetId="15" r:id="rId15"/>
-    <sheet name="All Nestos have Verilog File" sheetId="16" r:id="rId16"/>
-    <sheet name="Zero Length Verilog Files" sheetId="17" r:id="rId17"/>
-    <sheet name="Verilog Checker" sheetId="18" r:id="rId18"/>
-    <sheet name="DRM Efficiency" sheetId="19" r:id="rId19"/>
-    <sheet name="DRM Efficiency Summary" sheetId="20" r:id="rId20"/>
-    <sheet name="DFT Efficiency" sheetId="21" r:id="rId21"/>
-    <sheet name="DFM Efficiency Summary" sheetId="22" r:id="rId22"/>
-    <sheet name="Project Summary" sheetId="23" r:id="rId23"/>
-    <sheet name="Design Params and Codes" sheetId="24" r:id="rId24"/>
-    <sheet name="DRM Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="Register Summary" sheetId="26" r:id="rId26"/>
-    <sheet name="DFT Summary" sheetId="27" r:id="rId27"/>
-    <sheet name="Nesto Usage Report" sheetId="28" r:id="rId28"/>
+    <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
+    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
+    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
+    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
+    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
+    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
+    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
+    <sheet name="Symbol Length Exceed Max" sheetId="13" r:id="rId13"/>
+    <sheet name="Cell Length Exceed Max 50" sheetId="14" r:id="rId14"/>
+    <sheet name="All Nestos have Verilog File" sheetId="15" r:id="rId15"/>
+    <sheet name="Zero Length Verilog Files" sheetId="16" r:id="rId16"/>
+    <sheet name="Verilog Checker" sheetId="17" r:id="rId17"/>
+    <sheet name="DRM Efficiency" sheetId="18" r:id="rId18"/>
+    <sheet name="DRM Efficiency Summary" sheetId="19" r:id="rId19"/>
+    <sheet name="DFT Efficiency" sheetId="20" r:id="rId20"/>
+    <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
+    <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
+    <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
+    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
+    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="485" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="336">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -70,16 +69,13 @@
     <t>Xdatamap1 (datamap.function) missing expected field datamap_function_2</t>
   </si>
   <si>
-    <t>Missing Bio Symbol Files</t>
-  </si>
-  <si>
-    <t>No missing bio or symbol files...</t>
-  </si>
-  <si>
     <t>Missing Nets</t>
   </si>
   <si>
-    <t>All symbols have nets.</t>
+    <t>(!!! MUST FIX !!! - makes Corrupted Verilogs)</t>
+  </si>
+  <si>
+    <t>Xoscillator1,CELREF</t>
   </si>
   <si>
     <t>Shorted Inputs</t>
@@ -97,13 +93,7 @@
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>(!!! MUST FIX !!! - not allowed)</t>
-  </si>
-  <si>
-    <t>XCLOCK</t>
-  </si>
-  <si>
-    <t>Floating pin XMAIN.CELREF84329(CELREF84329)</t>
+    <t>No Floating Input Nets found.</t>
   </si>
   <si>
     <t>Floating Outputs</t>
@@ -116,9 +106,6 @@
   </si>
   <si>
     <t>No Connects - Inputs</t>
-  </si>
-  <si>
-    <t>CELREF84329 - {"path": "XCLOCK,XMAIN", "instance": "XMAIN", "symbol": "CELREF84329", "io": "input", "bus": "", "type": "child"}</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -416,25 +403,25 @@
     <t>gen_reports</t>
   </si>
   <si>
+    <t>pad_esd</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>find_isos</t>
+  </si>
+  <si>
+    <t>wipe_bio_symbol</t>
+  </si>
+  <si>
+    <t>workers</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>skip_serdes</t>
-  </si>
-  <si>
-    <t>pad_esd</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>find_isos</t>
-  </si>
-  <si>
-    <t>wipe_bio_symbol</t>
-  </si>
-  <si>
-    <t>workers</t>
-  </si>
-  <si>
-    <t>8</t>
   </si>
   <si>
     <t>Package</t>
@@ -1430,22 +1417,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>25</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1455,17 +1437,27 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1475,27 +1467,17 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1510,12 +1492,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1530,12 +1512,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1550,12 +1532,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1570,12 +1552,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>31</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1585,17 +1567,132 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -1605,132 +1702,17 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1740,17 +1722,22 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1795,22 +1782,17 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>63</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1820,17 +1802,22 @@
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1845,17 +1832,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>
@@ -1865,22 +1852,1355 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B180"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="5" spans="1:1">
+      <c r="B4" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>74</v>
+      </c>
+      <c r="B9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="1" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>87</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>93</v>
+      </c>
+      <c r="B29" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>95</v>
+      </c>
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>97</v>
+      </c>
+      <c r="B31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B32" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>99</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>103</v>
+      </c>
+      <c r="B35" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>105</v>
+      </c>
+      <c r="B36" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>108</v>
+      </c>
+      <c r="B38" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>111</v>
+      </c>
+      <c r="B41" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>112</v>
+      </c>
+      <c r="B42" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>116</v>
+      </c>
+      <c r="B46" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>118</v>
+      </c>
+      <c r="B47" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>119</v>
+      </c>
+      <c r="B48" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>121</v>
+      </c>
+      <c r="B49" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>122</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>123</v>
+      </c>
+      <c r="B51" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>125</v>
+      </c>
+      <c r="B52" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>129</v>
+      </c>
+      <c r="B56" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>131</v>
+      </c>
+      <c r="B57" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>143</v>
+      </c>
+      <c r="B68" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>145</v>
+      </c>
+      <c r="B69" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>146</v>
+      </c>
+      <c r="B70" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>152</v>
+      </c>
+      <c r="B77" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>153</v>
+      </c>
+      <c r="B78" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>154</v>
+      </c>
+      <c r="B79" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>157</v>
+      </c>
+      <c r="B81" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>159</v>
+      </c>
+      <c r="B82" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>160</v>
+      </c>
+      <c r="B83" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>161</v>
+      </c>
+      <c r="B84" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>162</v>
+      </c>
+      <c r="B85" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>163</v>
+      </c>
+      <c r="B86" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>164</v>
+      </c>
+      <c r="B87" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>165</v>
+      </c>
+      <c r="B88" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>166</v>
+      </c>
+      <c r="B89" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>167</v>
+      </c>
+      <c r="B90" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>169</v>
+      </c>
+      <c r="B91" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>170</v>
+      </c>
+      <c r="B92" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>171</v>
+      </c>
+      <c r="B93" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>172</v>
+      </c>
+      <c r="B94" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>173</v>
+      </c>
+      <c r="B95" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>174</v>
+      </c>
+      <c r="B96" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>175</v>
+      </c>
+      <c r="B97" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>177</v>
+      </c>
+      <c r="B99" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>178</v>
+      </c>
+      <c r="B100" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>179</v>
+      </c>
+      <c r="B101" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>180</v>
+      </c>
+      <c r="B102" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>181</v>
+      </c>
+      <c r="B103" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" s="1" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" t="s">
+        <v>183</v>
+      </c>
+      <c r="B106" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>185</v>
+      </c>
+      <c r="B107" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>187</v>
+      </c>
+      <c r="B108" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>189</v>
+      </c>
+      <c r="B109" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>191</v>
+      </c>
+      <c r="B110" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>193</v>
+      </c>
+      <c r="B111" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>195</v>
+      </c>
+      <c r="B112" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>197</v>
+      </c>
+      <c r="B113" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" t="s">
+        <v>199</v>
+      </c>
+      <c r="B116" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>200</v>
+      </c>
+      <c r="B117" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>202</v>
+      </c>
+      <c r="B118" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>204</v>
+      </c>
+      <c r="B119" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>206</v>
+      </c>
+      <c r="B120" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>208</v>
+      </c>
+      <c r="B121" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>210</v>
+      </c>
+      <c r="B122" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>212</v>
+      </c>
+      <c r="B123" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>213</v>
+      </c>
+      <c r="B124" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>214</v>
+      </c>
+      <c r="B125" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>215</v>
+      </c>
+      <c r="B126" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>217</v>
+      </c>
+      <c r="B127" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>219</v>
+      </c>
+      <c r="B128" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>221</v>
+      </c>
+      <c r="B129" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>223</v>
+      </c>
+      <c r="B130" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>176</v>
+      </c>
+      <c r="B131" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>177</v>
+      </c>
+      <c r="B132" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>179</v>
+      </c>
+      <c r="B133" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>178</v>
+      </c>
+      <c r="B134" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>229</v>
+      </c>
+      <c r="B135" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>230</v>
+      </c>
+      <c r="B136" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>232</v>
+      </c>
+      <c r="B137" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>234</v>
+      </c>
+      <c r="B138" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>236</v>
+      </c>
+      <c r="B139" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>238</v>
+      </c>
+      <c r="B140" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>240</v>
+      </c>
+      <c r="B141" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>241</v>
+      </c>
+      <c r="B142" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>242</v>
+      </c>
+      <c r="B143" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>243</v>
+      </c>
+      <c r="B144" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>244</v>
+      </c>
+      <c r="B145" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>245</v>
+      </c>
+      <c r="B146" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>246</v>
+      </c>
+      <c r="B147" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>247</v>
+      </c>
+      <c r="B148" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>248</v>
+      </c>
+      <c r="B149" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>250</v>
+      </c>
+      <c r="B150" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>252</v>
+      </c>
+      <c r="B151" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>254</v>
+      </c>
+      <c r="B152" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>256</v>
+      </c>
+      <c r="B153" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>258</v>
+      </c>
+      <c r="B154" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>260</v>
+      </c>
+      <c r="B155" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>262</v>
+      </c>
+      <c r="B156" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>264</v>
+      </c>
+      <c r="B157" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>266</v>
+      </c>
+      <c r="B158" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>268</v>
+      </c>
+      <c r="B159" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>270</v>
+      </c>
+      <c r="B160" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>272</v>
+      </c>
+      <c r="B161" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>274</v>
+      </c>
+      <c r="B162" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>276</v>
+      </c>
+      <c r="B163" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>278</v>
+      </c>
+      <c r="B164" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>280</v>
+      </c>
+      <c r="B165" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>282</v>
+      </c>
+      <c r="B166" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" t="s">
+        <v>283</v>
+      </c>
+      <c r="B167" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>284</v>
+      </c>
+      <c r="B168" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>285</v>
+      </c>
+      <c r="B169" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>287</v>
+      </c>
+      <c r="B170" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>289</v>
+      </c>
+      <c r="B171" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" t="s">
+        <v>291</v>
+      </c>
+      <c r="B172" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>293</v>
+      </c>
+      <c r="B173" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" t="s">
+        <v>295</v>
+      </c>
+      <c r="B174" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>296</v>
+      </c>
+      <c r="B175" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
+        <v>297</v>
+      </c>
+      <c r="B176" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>298</v>
+      </c>
+      <c r="B177" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" t="s">
+        <v>299</v>
+      </c>
+      <c r="B178" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" t="s">
+        <v>300</v>
+      </c>
+      <c r="B179" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" t="s">
+        <v>302</v>
+      </c>
+      <c r="B180" t="s">
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -1890,1355 +3210,76 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B180"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>71</v>
+        <v>305</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>73</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B6" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>306</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>76</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>77</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>78</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>80</v>
-      </c>
-      <c r="B10" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>90</v>
-      </c>
-      <c r="B20" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B21" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>95</v>
-      </c>
-      <c r="B27" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>96</v>
-      </c>
-      <c r="B28" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>97</v>
-      </c>
-      <c r="B29" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>99</v>
-      </c>
-      <c r="B30" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>101</v>
-      </c>
-      <c r="B31" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>102</v>
-      </c>
-      <c r="B32" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>103</v>
-      </c>
-      <c r="B33" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>105</v>
-      </c>
-      <c r="B34" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>107</v>
-      </c>
-      <c r="B35" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>109</v>
-      </c>
-      <c r="B36" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>112</v>
-      </c>
-      <c r="B38" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>113</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>114</v>
-      </c>
-      <c r="B40" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>115</v>
-      </c>
-      <c r="B41" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>116</v>
-      </c>
-      <c r="B42" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>117</v>
-      </c>
-      <c r="B43" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>120</v>
-      </c>
-      <c r="B46" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>122</v>
-      </c>
-      <c r="B47" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>123</v>
-      </c>
-      <c r="B48" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>124</v>
-      </c>
-      <c r="B49" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>126</v>
-      </c>
-      <c r="B50" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>127</v>
-      </c>
-      <c r="B51" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>128</v>
-      </c>
-      <c r="B52" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="1" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>131</v>
-      </c>
-      <c r="B55" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>133</v>
-      </c>
-      <c r="B56" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>135</v>
-      </c>
-      <c r="B57" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>141</v>
-      </c>
-      <c r="B64" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>145</v>
-      </c>
-      <c r="B67" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>147</v>
-      </c>
-      <c r="B68" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>149</v>
-      </c>
-      <c r="B69" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>150</v>
-      </c>
-      <c r="B70" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="1" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" t="s">
-        <v>156</v>
-      </c>
-      <c r="B77" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" t="s">
-        <v>157</v>
-      </c>
-      <c r="B78" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" t="s">
-        <v>158</v>
-      </c>
-      <c r="B79" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" t="s">
-        <v>159</v>
-      </c>
-      <c r="B80" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" t="s">
-        <v>161</v>
-      </c>
-      <c r="B81" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
-        <v>163</v>
-      </c>
-      <c r="B82" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" t="s">
-        <v>164</v>
-      </c>
-      <c r="B83" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" t="s">
-        <v>165</v>
-      </c>
-      <c r="B84" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" t="s">
-        <v>166</v>
-      </c>
-      <c r="B85" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" t="s">
-        <v>167</v>
-      </c>
-      <c r="B86" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" t="s">
-        <v>168</v>
-      </c>
-      <c r="B87" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" t="s">
-        <v>169</v>
-      </c>
-      <c r="B88" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" t="s">
-        <v>170</v>
-      </c>
-      <c r="B89" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" t="s">
-        <v>171</v>
-      </c>
-      <c r="B90" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" t="s">
-        <v>173</v>
-      </c>
-      <c r="B91" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" t="s">
-        <v>174</v>
-      </c>
-      <c r="B92" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" t="s">
-        <v>175</v>
-      </c>
-      <c r="B93" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" t="s">
-        <v>176</v>
-      </c>
-      <c r="B94" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
-        <v>177</v>
-      </c>
-      <c r="B95" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" t="s">
-        <v>178</v>
-      </c>
-      <c r="B96" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" t="s">
-        <v>179</v>
-      </c>
-      <c r="B97" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" t="s">
-        <v>180</v>
-      </c>
-      <c r="B98" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" t="s">
-        <v>181</v>
-      </c>
-      <c r="B99" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
-        <v>182</v>
-      </c>
-      <c r="B100" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
-        <v>183</v>
-      </c>
-      <c r="B101" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>184</v>
-      </c>
-      <c r="B102" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>185</v>
-      </c>
-      <c r="B103" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" t="s">
-        <v>187</v>
-      </c>
-      <c r="B106" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" t="s">
-        <v>189</v>
-      </c>
-      <c r="B107" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" t="s">
-        <v>191</v>
-      </c>
-      <c r="B108" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" t="s">
-        <v>193</v>
-      </c>
-      <c r="B109" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" t="s">
-        <v>195</v>
-      </c>
-      <c r="B110" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" t="s">
-        <v>197</v>
-      </c>
-      <c r="B111" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" t="s">
-        <v>199</v>
-      </c>
-      <c r="B112" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" t="s">
-        <v>201</v>
-      </c>
-      <c r="B113" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="1" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" t="s">
-        <v>203</v>
-      </c>
-      <c r="B116" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" t="s">
-        <v>204</v>
-      </c>
-      <c r="B117" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" t="s">
-        <v>206</v>
-      </c>
-      <c r="B118" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" t="s">
-        <v>208</v>
-      </c>
-      <c r="B119" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" t="s">
-        <v>210</v>
-      </c>
-      <c r="B120" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" t="s">
-        <v>212</v>
-      </c>
-      <c r="B121" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" t="s">
-        <v>214</v>
-      </c>
-      <c r="B122" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" t="s">
-        <v>216</v>
-      </c>
-      <c r="B123" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" t="s">
-        <v>217</v>
-      </c>
-      <c r="B124" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" t="s">
-        <v>218</v>
-      </c>
-      <c r="B125" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" t="s">
-        <v>219</v>
-      </c>
-      <c r="B126" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" t="s">
-        <v>221</v>
-      </c>
-      <c r="B127" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" t="s">
-        <v>223</v>
-      </c>
-      <c r="B128" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" t="s">
-        <v>225</v>
-      </c>
-      <c r="B129" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" t="s">
-        <v>227</v>
-      </c>
-      <c r="B130" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" t="s">
-        <v>180</v>
-      </c>
-      <c r="B131" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" t="s">
-        <v>181</v>
-      </c>
-      <c r="B132" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" t="s">
-        <v>183</v>
-      </c>
-      <c r="B133" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" t="s">
-        <v>182</v>
-      </c>
-      <c r="B134" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" t="s">
-        <v>233</v>
-      </c>
-      <c r="B135" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" t="s">
-        <v>234</v>
-      </c>
-      <c r="B136" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" t="s">
-        <v>236</v>
-      </c>
-      <c r="B137" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" t="s">
-        <v>238</v>
-      </c>
-      <c r="B138" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" t="s">
-        <v>240</v>
-      </c>
-      <c r="B139" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" t="s">
-        <v>242</v>
-      </c>
-      <c r="B140" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" t="s">
-        <v>244</v>
-      </c>
-      <c r="B141" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" t="s">
-        <v>245</v>
-      </c>
-      <c r="B142" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" t="s">
-        <v>246</v>
-      </c>
-      <c r="B143" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" t="s">
-        <v>247</v>
-      </c>
-      <c r="B144" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" t="s">
-        <v>248</v>
-      </c>
-      <c r="B145" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" t="s">
-        <v>249</v>
-      </c>
-      <c r="B146" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" t="s">
-        <v>250</v>
-      </c>
-      <c r="B147" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" t="s">
-        <v>251</v>
-      </c>
-      <c r="B148" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" t="s">
-        <v>252</v>
-      </c>
-      <c r="B149" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" t="s">
-        <v>254</v>
-      </c>
-      <c r="B150" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" t="s">
-        <v>256</v>
-      </c>
-      <c r="B151" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" t="s">
-        <v>258</v>
-      </c>
-      <c r="B152" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" t="s">
-        <v>260</v>
-      </c>
-      <c r="B153" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" t="s">
-        <v>262</v>
-      </c>
-      <c r="B154" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" t="s">
-        <v>264</v>
-      </c>
-      <c r="B155" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" t="s">
-        <v>266</v>
-      </c>
-      <c r="B156" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" t="s">
-        <v>268</v>
-      </c>
-      <c r="B157" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" t="s">
-        <v>270</v>
-      </c>
-      <c r="B158" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" t="s">
-        <v>272</v>
-      </c>
-      <c r="B159" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" t="s">
-        <v>274</v>
-      </c>
-      <c r="B160" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" t="s">
-        <v>276</v>
-      </c>
-      <c r="B161" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" t="s">
-        <v>278</v>
-      </c>
-      <c r="B162" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" t="s">
-        <v>280</v>
-      </c>
-      <c r="B163" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" t="s">
-        <v>282</v>
-      </c>
-      <c r="B164" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" t="s">
-        <v>284</v>
-      </c>
-      <c r="B165" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" t="s">
-        <v>286</v>
-      </c>
-      <c r="B166" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" t="s">
-        <v>287</v>
-      </c>
-      <c r="B167" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" t="s">
-        <v>288</v>
-      </c>
-      <c r="B168" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" t="s">
-        <v>289</v>
-      </c>
-      <c r="B169" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" t="s">
-        <v>291</v>
-      </c>
-      <c r="B170" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" t="s">
-        <v>293</v>
-      </c>
-      <c r="B171" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" t="s">
-        <v>295</v>
-      </c>
-      <c r="B172" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" t="s">
-        <v>297</v>
-      </c>
-      <c r="B173" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" t="s">
-        <v>299</v>
-      </c>
-      <c r="B174" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" t="s">
-        <v>300</v>
-      </c>
-      <c r="B175" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" t="s">
-        <v>301</v>
-      </c>
-      <c r="B176" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" t="s">
-        <v>302</v>
-      </c>
-      <c r="B177" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" t="s">
-        <v>303</v>
-      </c>
-      <c r="B178" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" t="s">
-        <v>304</v>
-      </c>
-      <c r="B179" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" t="s">
-        <v>306</v>
-      </c>
-      <c r="B180" t="s">
-        <v>241</v>
+        <v>315</v>
       </c>
     </row>
   </sheetData>
@@ -3248,76 +3289,12 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>312</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
         <v>316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -3327,12 +3304,31 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3342,46 +3338,12 @@
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3391,114 +3353,114 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B5" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B6" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B7" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B9" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B10" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B11" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B12" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B13" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B14" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B15" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B16" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B17" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3508,7 +3470,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3524,6 +3486,16 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3538,7 +3510,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3548,7 +3520,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -3563,7 +3535,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3573,7 +3545,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -3588,7 +3560,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3598,7 +3570,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3608,12 +3580,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" spans="1:1">
@@ -3623,17 +3595,7 @@
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="1" t="s">
         <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -3643,22 +3605,17 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -3673,7 +3630,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">

--- a/TELEMETRYadcCLOCK/project/Summary.xlsx
+++ b/TELEMETRYadcCLOCK/project/Summary.xlsx
@@ -10,37 +10,36 @@
     <sheet name="No Zero Net" sheetId="1" r:id="rId1"/>
     <sheet name="Validate no &quot;text&quot; in Datamaps" sheetId="2" r:id="rId2"/>
     <sheet name="Missing Nets" sheetId="3" r:id="rId3"/>
-    <sheet name="Shorted Inputs" sheetId="4" r:id="rId4"/>
-    <sheet name="Shorted Outputs" sheetId="5" r:id="rId5"/>
-    <sheet name="Floating Inputs" sheetId="6" r:id="rId6"/>
-    <sheet name="Floating Outputs" sheetId="7" r:id="rId7"/>
-    <sheet name="No Connects - Outputs" sheetId="8" r:id="rId8"/>
-    <sheet name="No Connects - Inputs" sheetId="9" r:id="rId9"/>
-    <sheet name="Mixed Mode Conflicts" sheetId="10" r:id="rId10"/>
-    <sheet name="Ring Core IO check report" sheetId="11" r:id="rId11"/>
-    <sheet name="D to A Tree" sheetId="12" r:id="rId12"/>
-    <sheet name="Symbol Length Exceed Max" sheetId="13" r:id="rId13"/>
-    <sheet name="Cell Length Exceed Max 50" sheetId="14" r:id="rId14"/>
-    <sheet name="All Nestos have Verilog File" sheetId="15" r:id="rId15"/>
-    <sheet name="Zero Length Verilog Files" sheetId="16" r:id="rId16"/>
-    <sheet name="Verilog Checker" sheetId="17" r:id="rId17"/>
-    <sheet name="DRM Efficiency" sheetId="18" r:id="rId18"/>
-    <sheet name="DRM Efficiency Summary" sheetId="19" r:id="rId19"/>
-    <sheet name="DFT Efficiency" sheetId="20" r:id="rId20"/>
-    <sheet name="DFM Efficiency Summary" sheetId="21" r:id="rId21"/>
-    <sheet name="Project Summary" sheetId="22" r:id="rId22"/>
-    <sheet name="Design Params and Codes" sheetId="23" r:id="rId23"/>
-    <sheet name="DRM Summary" sheetId="24" r:id="rId24"/>
-    <sheet name="Register Summary" sheetId="25" r:id="rId25"/>
-    <sheet name="DFT Summary" sheetId="26" r:id="rId26"/>
-    <sheet name="Nesto Usage Report" sheetId="27" r:id="rId27"/>
+    <sheet name="Shorted Nets" sheetId="4" r:id="rId4"/>
+    <sheet name="Floating Inputs" sheetId="5" r:id="rId5"/>
+    <sheet name="Floating Outputs" sheetId="6" r:id="rId6"/>
+    <sheet name="No Connects - Customer" sheetId="7" r:id="rId7"/>
+    <sheet name="No Connects - Celera" sheetId="8" r:id="rId8"/>
+    <sheet name="Mixed Mode Conflicts" sheetId="9" r:id="rId9"/>
+    <sheet name="Ring Core IO check report" sheetId="10" r:id="rId10"/>
+    <sheet name="D to A Tree" sheetId="11" r:id="rId11"/>
+    <sheet name="Symbol Length Exceed Max" sheetId="12" r:id="rId12"/>
+    <sheet name="Cell Length Exceed Max 50" sheetId="13" r:id="rId13"/>
+    <sheet name="All Nestos have Verilog File" sheetId="14" r:id="rId14"/>
+    <sheet name="Zero Length Verilog Files" sheetId="15" r:id="rId15"/>
+    <sheet name="Verilog Checker" sheetId="16" r:id="rId16"/>
+    <sheet name="DRM Efficiency" sheetId="17" r:id="rId17"/>
+    <sheet name="DRM Efficiency Summary" sheetId="18" r:id="rId18"/>
+    <sheet name="DFT Efficiency" sheetId="19" r:id="rId19"/>
+    <sheet name="DFM Efficiency Summary" sheetId="20" r:id="rId20"/>
+    <sheet name="Project Summary" sheetId="21" r:id="rId21"/>
+    <sheet name="Design Params and Codes" sheetId="22" r:id="rId22"/>
+    <sheet name="DRM Summary" sheetId="23" r:id="rId23"/>
+    <sheet name="Register Summary" sheetId="24" r:id="rId24"/>
+    <sheet name="DFT Summary" sheetId="25" r:id="rId25"/>
+    <sheet name="Nesto Usage Report" sheetId="26" r:id="rId26"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="339">
   <si>
     <t>No Zero Net</t>
   </si>
@@ -78,34 +77,40 @@
     <t>Xoscillator1,CELREF</t>
   </si>
   <si>
-    <t>Shorted Inputs</t>
-  </si>
-  <si>
-    <t>No Shorted Input Nets found.</t>
-  </si>
-  <si>
-    <t>Shorted Outputs</t>
-  </si>
-  <si>
-    <t>No Shorted Output Nets found.</t>
+    <t>Shorted Nets</t>
+  </si>
+  <si>
+    <t>No Shorted Nets found.</t>
   </si>
   <si>
     <t>Floating Inputs</t>
   </si>
   <si>
-    <t>No Floating Input Nets found.</t>
+    <t>(!!! MUST FIX !!! - not allowed)</t>
+  </si>
+  <si>
+    <t>XCLOCK,XDEBUG</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.dft_clock(dft_clock)</t>
+  </si>
+  <si>
+    <t>Floating pin XDEBUG.fault_adcclock(fault_adcclock)</t>
+  </si>
+  <si>
+    <t>Floating pin Xoscillator1.global_oscillatorring(tl0)</t>
   </si>
   <si>
     <t>Floating Outputs</t>
   </si>
   <si>
-    <t>No Floating Output Nets found.</t>
-  </si>
-  <si>
-    <t>No Connects - Outputs</t>
-  </si>
-  <si>
-    <t>No Connects - Inputs</t>
+    <t>No Connects - Customer</t>
+  </si>
+  <si>
+    <t>No Connects - Celera</t>
+  </si>
+  <si>
+    <t>XU1.pulse net: XUADCCLOCKstartup_no_dft_noconn_pulse io: output</t>
   </si>
   <si>
     <t>Mixed Mode Conflicts</t>
@@ -502,6 +507,9 @@
     <t>Register</t>
   </si>
   <si>
+    <t>registermap_buswidth</t>
+  </si>
+  <si>
     <t>registermap_security</t>
   </si>
   <si>
@@ -1021,37 +1029,37 @@
     <t>dbuf</t>
   </si>
   <si>
+    <t>inv</t>
+  </si>
+  <si>
+    <t>wrapper</t>
+  </si>
+  <si>
+    <t>oscillatorring</t>
+  </si>
+  <si>
     <t>noconn</t>
   </si>
   <si>
-    <t>inv</t>
+    <t>nand2</t>
+  </si>
+  <si>
+    <t>dmux4</t>
+  </si>
+  <si>
+    <t>delayclock</t>
+  </si>
+  <si>
+    <t>decoder2</t>
+  </si>
+  <si>
+    <t>datamap0</t>
+  </si>
+  <si>
+    <t>clockrequest</t>
   </si>
   <si>
     <t>PEBBLEtielo</t>
-  </si>
-  <si>
-    <t>wrapper</t>
-  </si>
-  <si>
-    <t>oscillatorring</t>
-  </si>
-  <si>
-    <t>nand2</t>
-  </si>
-  <si>
-    <t>dmux4</t>
-  </si>
-  <si>
-    <t>delayclock</t>
-  </si>
-  <si>
-    <t>decoder2</t>
-  </si>
-  <si>
-    <t>datamap0</t>
-  </si>
-  <si>
-    <t>clockrequest</t>
   </si>
 </sst>
 </file>
@@ -1417,17 +1425,27 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1437,27 +1455,17 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1472,12 +1480,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1492,12 +1500,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1512,12 +1520,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1532,12 +1540,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>27</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1547,17 +1555,132 @@
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1567,132 +1690,17 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="1" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="1" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="1" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="1" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
-      <c r="A33" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
-      <c r="A37" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
-      <c r="A39" s="1" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
-      <c r="A41" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
-      <c r="A43" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
-      <c r="A46" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
-      <c r="A48" t="s">
-        <v>55</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1702,17 +1710,22 @@
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1722,22 +1735,17 @@
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1782,17 +1790,22 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1807,17 +1820,17 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -1827,22 +1840,1363 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:B181"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>64</v>
+        <v>71</v>
+      </c>
+      <c r="B5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B6" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>75</v>
+      </c>
+      <c r="B8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>76</v>
+      </c>
+      <c r="B9" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" t="s">
+        <v>88</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" t="s">
+        <v>89</v>
+      </c>
+      <c r="B21" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" t="s">
+        <v>93</v>
+      </c>
+      <c r="B27" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" t="s">
+        <v>94</v>
+      </c>
+      <c r="B28" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" t="s">
+        <v>95</v>
+      </c>
+      <c r="B29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" t="s">
+        <v>97</v>
+      </c>
+      <c r="B30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" t="s">
+        <v>101</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" t="s">
+        <v>103</v>
+      </c>
+      <c r="B34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" t="s">
+        <v>105</v>
+      </c>
+      <c r="B35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" t="s">
+        <v>111</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" t="s">
+        <v>112</v>
+      </c>
+      <c r="B40" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43" t="s">
+        <v>115</v>
+      </c>
+      <c r="B43" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46" t="s">
+        <v>118</v>
+      </c>
+      <c r="B46" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47" t="s">
+        <v>120</v>
+      </c>
+      <c r="B47" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48" t="s">
+        <v>121</v>
+      </c>
+      <c r="B48" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49" t="s">
+        <v>123</v>
+      </c>
+      <c r="B49" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50" t="s">
+        <v>124</v>
+      </c>
+      <c r="B50" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51" t="s">
+        <v>125</v>
+      </c>
+      <c r="B51" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52" t="s">
+        <v>127</v>
+      </c>
+      <c r="B52" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55" t="s">
+        <v>129</v>
+      </c>
+      <c r="B55" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56" t="s">
+        <v>131</v>
+      </c>
+      <c r="B56" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57" t="s">
+        <v>133</v>
+      </c>
+      <c r="B57" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>139</v>
+      </c>
+      <c r="B64" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68" t="s">
+        <v>145</v>
+      </c>
+      <c r="B68" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>147</v>
+      </c>
+      <c r="B69" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70" t="s">
+        <v>148</v>
+      </c>
+      <c r="B70" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2">
+      <c r="A72" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2">
+      <c r="A73" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>154</v>
+      </c>
+      <c r="B77" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>155</v>
+      </c>
+      <c r="B78" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>157</v>
+      </c>
+      <c r="B80" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" t="s">
+        <v>158</v>
+      </c>
+      <c r="B81" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" t="s">
+        <v>160</v>
+      </c>
+      <c r="B82" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2">
+      <c r="A83" t="s">
+        <v>162</v>
+      </c>
+      <c r="B83" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2">
+      <c r="A84" t="s">
+        <v>163</v>
+      </c>
+      <c r="B84" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2">
+      <c r="A85" t="s">
+        <v>164</v>
+      </c>
+      <c r="B85" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2">
+      <c r="A86" t="s">
+        <v>165</v>
+      </c>
+      <c r="B86" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2">
+      <c r="A87" t="s">
+        <v>166</v>
+      </c>
+      <c r="B87" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2">
+      <c r="A88" t="s">
+        <v>167</v>
+      </c>
+      <c r="B88" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2">
+      <c r="A89" t="s">
+        <v>168</v>
+      </c>
+      <c r="B89" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2">
+      <c r="A90" t="s">
+        <v>169</v>
+      </c>
+      <c r="B90" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2">
+      <c r="A91" t="s">
+        <v>170</v>
+      </c>
+      <c r="B91" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2">
+      <c r="A92" t="s">
+        <v>172</v>
+      </c>
+      <c r="B92" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2">
+      <c r="A93" t="s">
+        <v>173</v>
+      </c>
+      <c r="B93" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2">
+      <c r="A94" t="s">
+        <v>174</v>
+      </c>
+      <c r="B94" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2">
+      <c r="A95" t="s">
+        <v>175</v>
+      </c>
+      <c r="B95" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2">
+      <c r="A96" t="s">
+        <v>176</v>
+      </c>
+      <c r="B96" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2">
+      <c r="A97" t="s">
+        <v>177</v>
+      </c>
+      <c r="B97" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2">
+      <c r="A98" t="s">
+        <v>178</v>
+      </c>
+      <c r="B98" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2">
+      <c r="A99" t="s">
+        <v>179</v>
+      </c>
+      <c r="B99" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" t="s">
+        <v>180</v>
+      </c>
+      <c r="B100" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2">
+      <c r="A101" t="s">
+        <v>181</v>
+      </c>
+      <c r="B101" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2">
+      <c r="A102" t="s">
+        <v>182</v>
+      </c>
+      <c r="B102" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2">
+      <c r="A103" t="s">
+        <v>183</v>
+      </c>
+      <c r="B103" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2">
+      <c r="A104" t="s">
+        <v>184</v>
+      </c>
+      <c r="B104" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2">
+      <c r="A105" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2">
+      <c r="A106" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2">
+      <c r="A107" t="s">
+        <v>186</v>
+      </c>
+      <c r="B107" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2">
+      <c r="A108" t="s">
+        <v>188</v>
+      </c>
+      <c r="B108" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2">
+      <c r="A109" t="s">
+        <v>190</v>
+      </c>
+      <c r="B109" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2">
+      <c r="A110" t="s">
+        <v>192</v>
+      </c>
+      <c r="B110" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2">
+      <c r="A111" t="s">
+        <v>194</v>
+      </c>
+      <c r="B111" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2">
+      <c r="A112" t="s">
+        <v>196</v>
+      </c>
+      <c r="B112" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2">
+      <c r="A113" t="s">
+        <v>198</v>
+      </c>
+      <c r="B113" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2">
+      <c r="A114" t="s">
+        <v>200</v>
+      </c>
+      <c r="B114" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2">
+      <c r="A115" s="1" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2">
+      <c r="A116" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2">
+      <c r="A117" t="s">
+        <v>202</v>
+      </c>
+      <c r="B117" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2">
+      <c r="A118" t="s">
+        <v>203</v>
+      </c>
+      <c r="B118" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2">
+      <c r="A119" t="s">
+        <v>205</v>
+      </c>
+      <c r="B119" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2">
+      <c r="A120" t="s">
+        <v>207</v>
+      </c>
+      <c r="B120" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2">
+      <c r="A121" t="s">
+        <v>209</v>
+      </c>
+      <c r="B121" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2">
+      <c r="A122" t="s">
+        <v>211</v>
+      </c>
+      <c r="B122" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2">
+      <c r="A123" t="s">
+        <v>213</v>
+      </c>
+      <c r="B123" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2">
+      <c r="A124" t="s">
+        <v>215</v>
+      </c>
+      <c r="B124" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2">
+      <c r="A125" t="s">
+        <v>216</v>
+      </c>
+      <c r="B125" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2">
+      <c r="A126" t="s">
+        <v>217</v>
+      </c>
+      <c r="B126" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2">
+      <c r="A127" t="s">
+        <v>218</v>
+      </c>
+      <c r="B127" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2">
+      <c r="A128" t="s">
+        <v>220</v>
+      </c>
+      <c r="B128" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2">
+      <c r="A129" t="s">
+        <v>222</v>
+      </c>
+      <c r="B129" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2">
+      <c r="A130" t="s">
+        <v>224</v>
+      </c>
+      <c r="B130" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2">
+      <c r="A131" t="s">
+        <v>226</v>
+      </c>
+      <c r="B131" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2">
+      <c r="A132" t="s">
+        <v>179</v>
+      </c>
+      <c r="B132" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2">
+      <c r="A133" t="s">
+        <v>180</v>
+      </c>
+      <c r="B133" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2">
+      <c r="A134" t="s">
+        <v>182</v>
+      </c>
+      <c r="B134" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2">
+      <c r="A135" t="s">
+        <v>181</v>
+      </c>
+      <c r="B135" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2">
+      <c r="A136" t="s">
+        <v>232</v>
+      </c>
+      <c r="B136" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2">
+      <c r="A137" t="s">
+        <v>233</v>
+      </c>
+      <c r="B137" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2">
+      <c r="A138" t="s">
+        <v>235</v>
+      </c>
+      <c r="B138" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2">
+      <c r="A139" t="s">
+        <v>237</v>
+      </c>
+      <c r="B139" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2">
+      <c r="A140" t="s">
+        <v>239</v>
+      </c>
+      <c r="B140" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2">
+      <c r="A141" t="s">
+        <v>241</v>
+      </c>
+      <c r="B141" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2">
+      <c r="A142" t="s">
+        <v>243</v>
+      </c>
+      <c r="B142" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2">
+      <c r="A143" t="s">
+        <v>244</v>
+      </c>
+      <c r="B143" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2">
+      <c r="A144" t="s">
+        <v>245</v>
+      </c>
+      <c r="B144" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2">
+      <c r="A145" t="s">
+        <v>246</v>
+      </c>
+      <c r="B145" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2">
+      <c r="A146" t="s">
+        <v>247</v>
+      </c>
+      <c r="B146" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2">
+      <c r="A147" t="s">
+        <v>248</v>
+      </c>
+      <c r="B147" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2">
+      <c r="A148" t="s">
+        <v>249</v>
+      </c>
+      <c r="B148" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2">
+      <c r="A149" t="s">
+        <v>250</v>
+      </c>
+      <c r="B149" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2">
+      <c r="A150" t="s">
+        <v>251</v>
+      </c>
+      <c r="B150" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2">
+      <c r="A151" t="s">
+        <v>253</v>
+      </c>
+      <c r="B151" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2">
+      <c r="A152" t="s">
+        <v>255</v>
+      </c>
+      <c r="B152" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2">
+      <c r="A153" t="s">
+        <v>257</v>
+      </c>
+      <c r="B153" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2">
+      <c r="A154" t="s">
+        <v>259</v>
+      </c>
+      <c r="B154" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2">
+      <c r="A155" t="s">
+        <v>261</v>
+      </c>
+      <c r="B155" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2">
+      <c r="A156" t="s">
+        <v>263</v>
+      </c>
+      <c r="B156" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2">
+      <c r="A157" t="s">
+        <v>265</v>
+      </c>
+      <c r="B157" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2">
+      <c r="A158" t="s">
+        <v>267</v>
+      </c>
+      <c r="B158" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2">
+      <c r="A159" t="s">
+        <v>269</v>
+      </c>
+      <c r="B159" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2">
+      <c r="A160" t="s">
+        <v>271</v>
+      </c>
+      <c r="B160" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2">
+      <c r="A161" t="s">
+        <v>273</v>
+      </c>
+      <c r="B161" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2">
+      <c r="A162" t="s">
+        <v>275</v>
+      </c>
+      <c r="B162" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2">
+      <c r="A163" t="s">
+        <v>277</v>
+      </c>
+      <c r="B163" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2">
+      <c r="A164" t="s">
+        <v>279</v>
+      </c>
+      <c r="B164" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2">
+      <c r="A165" t="s">
+        <v>281</v>
+      </c>
+      <c r="B165" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2">
+      <c r="A166" t="s">
+        <v>283</v>
+      </c>
+      <c r="B166" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2">
+      <c r="A167" t="s">
+        <v>285</v>
+      </c>
+      <c r="B167" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2">
+      <c r="A168" t="s">
+        <v>286</v>
+      </c>
+      <c r="B168" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2">
+      <c r="A169" t="s">
+        <v>287</v>
+      </c>
+      <c r="B169" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2">
+      <c r="A170" t="s">
+        <v>288</v>
+      </c>
+      <c r="B170" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2">
+      <c r="A171" t="s">
+        <v>290</v>
+      </c>
+      <c r="B171" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2">
+      <c r="A172" t="s">
+        <v>292</v>
+      </c>
+      <c r="B172" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2">
+      <c r="A173" t="s">
+        <v>294</v>
+      </c>
+      <c r="B173" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2">
+      <c r="A174" t="s">
+        <v>296</v>
+      </c>
+      <c r="B174" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2">
+      <c r="A175" t="s">
+        <v>298</v>
+      </c>
+      <c r="B175" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2">
+      <c r="A176" t="s">
+        <v>299</v>
+      </c>
+      <c r="B176" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2">
+      <c r="A177" t="s">
+        <v>300</v>
+      </c>
+      <c r="B177" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2">
+      <c r="A178" t="s">
+        <v>301</v>
+      </c>
+      <c r="B178" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2">
+      <c r="A179" t="s">
+        <v>302</v>
+      </c>
+      <c r="B179" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2">
+      <c r="A180" t="s">
+        <v>303</v>
+      </c>
+      <c r="B180" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2">
+      <c r="A181" t="s">
+        <v>305</v>
+      </c>
+      <c r="B181" t="s">
+        <v>240</v>
       </c>
     </row>
   </sheetData>
@@ -1852,1355 +3206,76 @@
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B180"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
       <c r="A3" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
       <c r="A4" s="1" t="s">
-        <v>67</v>
+        <v>308</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>71</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>309</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>72</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>73</v>
-      </c>
-      <c r="B8" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>74</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>78</v>
-      </c>
-      <c r="B11" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B12" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" t="s">
-        <v>87</v>
-      </c>
-      <c r="B21" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" t="s">
-        <v>91</v>
-      </c>
-      <c r="B27" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" t="s">
-        <v>92</v>
-      </c>
-      <c r="B28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" t="s">
-        <v>93</v>
-      </c>
-      <c r="B29" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" t="s">
-        <v>95</v>
-      </c>
-      <c r="B30" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" t="s">
-        <v>97</v>
-      </c>
-      <c r="B31" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" t="s">
-        <v>98</v>
-      </c>
-      <c r="B32" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" t="s">
-        <v>99</v>
-      </c>
-      <c r="B33" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" t="s">
-        <v>103</v>
-      </c>
-      <c r="B35" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" t="s">
-        <v>105</v>
-      </c>
-      <c r="B36" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" t="s">
-        <v>108</v>
-      </c>
-      <c r="B38" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" t="s">
-        <v>109</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" t="s">
-        <v>110</v>
-      </c>
-      <c r="B40" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41" t="s">
-        <v>111</v>
-      </c>
-      <c r="B41" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42" t="s">
-        <v>112</v>
-      </c>
-      <c r="B42" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43" t="s">
-        <v>113</v>
-      </c>
-      <c r="B43" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44" s="1" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46" t="s">
-        <v>116</v>
-      </c>
-      <c r="B46" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47" t="s">
-        <v>118</v>
-      </c>
-      <c r="B47" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48" t="s">
-        <v>119</v>
-      </c>
-      <c r="B48" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49" t="s">
-        <v>121</v>
-      </c>
-      <c r="B49" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50" t="s">
-        <v>122</v>
-      </c>
-      <c r="B50" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51" t="s">
-        <v>123</v>
-      </c>
-      <c r="B51" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52" t="s">
-        <v>125</v>
-      </c>
-      <c r="B52" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53" s="1" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55" t="s">
-        <v>127</v>
-      </c>
-      <c r="B55" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56" t="s">
-        <v>129</v>
-      </c>
-      <c r="B56" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57" t="s">
-        <v>131</v>
-      </c>
-      <c r="B57" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
-        <v>137</v>
-      </c>
-      <c r="B64" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67" t="s">
-        <v>141</v>
-      </c>
-      <c r="B67" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68" t="s">
-        <v>143</v>
-      </c>
-      <c r="B68" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2">
-      <c r="A72" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2">
-      <c r="A73" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2">
-      <c r="A74" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2">
-      <c r="A75" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2">
-      <c r="A76" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B76" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2">
-      <c r="A77" t="s">
-        <v>152</v>
-      </c>
-      <c r="B77" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2">
-      <c r="A78" t="s">
-        <v>153</v>
-      </c>
-      <c r="B78" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2">
-      <c r="A79" t="s">
-        <v>154</v>
-      </c>
-      <c r="B79" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2">
-      <c r="A80" t="s">
-        <v>155</v>
-      </c>
-      <c r="B80" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2">
-      <c r="A81" t="s">
-        <v>157</v>
-      </c>
-      <c r="B81" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2">
-      <c r="A82" t="s">
-        <v>159</v>
-      </c>
-      <c r="B82" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2">
-      <c r="A83" t="s">
-        <v>160</v>
-      </c>
-      <c r="B83" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2">
-      <c r="A84" t="s">
-        <v>161</v>
-      </c>
-      <c r="B84" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2">
-      <c r="A85" t="s">
-        <v>162</v>
-      </c>
-      <c r="B85" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2">
-      <c r="A86" t="s">
-        <v>163</v>
-      </c>
-      <c r="B86" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2">
-      <c r="A87" t="s">
-        <v>164</v>
-      </c>
-      <c r="B87" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2">
-      <c r="A88" t="s">
-        <v>165</v>
-      </c>
-      <c r="B88" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2">
-      <c r="A89" t="s">
-        <v>166</v>
-      </c>
-      <c r="B89" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2">
-      <c r="A90" t="s">
-        <v>167</v>
-      </c>
-      <c r="B90" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2">
-      <c r="A91" t="s">
-        <v>169</v>
-      </c>
-      <c r="B91" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2">
-      <c r="A92" t="s">
-        <v>170</v>
-      </c>
-      <c r="B92" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2">
-      <c r="A93" t="s">
-        <v>171</v>
-      </c>
-      <c r="B93" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2">
-      <c r="A94" t="s">
-        <v>172</v>
-      </c>
-      <c r="B94" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2">
-      <c r="A95" t="s">
-        <v>173</v>
-      </c>
-      <c r="B95" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2">
-      <c r="A96" t="s">
-        <v>174</v>
-      </c>
-      <c r="B96" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2">
-      <c r="A97" t="s">
-        <v>175</v>
-      </c>
-      <c r="B97" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2">
-      <c r="A98" t="s">
-        <v>176</v>
-      </c>
-      <c r="B98" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2">
-      <c r="A99" t="s">
-        <v>177</v>
-      </c>
-      <c r="B99" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2">
-      <c r="A100" t="s">
-        <v>178</v>
-      </c>
-      <c r="B100" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2">
-      <c r="A101" t="s">
-        <v>179</v>
-      </c>
-      <c r="B101" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2">
-      <c r="A102" t="s">
-        <v>180</v>
-      </c>
-      <c r="B102" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2">
-      <c r="A103" t="s">
-        <v>181</v>
-      </c>
-      <c r="B103" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2">
-      <c r="A104" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2">
-      <c r="A105" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B105" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2">
-      <c r="A106" t="s">
-        <v>183</v>
-      </c>
-      <c r="B106" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2">
-      <c r="A107" t="s">
-        <v>185</v>
-      </c>
-      <c r="B107" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2">
-      <c r="A108" t="s">
-        <v>187</v>
-      </c>
-      <c r="B108" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2">
-      <c r="A109" t="s">
-        <v>189</v>
-      </c>
-      <c r="B109" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2">
-      <c r="A110" t="s">
-        <v>191</v>
-      </c>
-      <c r="B110" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2">
-      <c r="A111" t="s">
-        <v>193</v>
-      </c>
-      <c r="B111" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2">
-      <c r="A112" t="s">
-        <v>195</v>
-      </c>
-      <c r="B112" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2">
-      <c r="A113" t="s">
-        <v>197</v>
-      </c>
-      <c r="B113" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2">
-      <c r="A114" s="1" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2">
-      <c r="A115" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2">
-      <c r="A116" t="s">
-        <v>199</v>
-      </c>
-      <c r="B116" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2">
-      <c r="A117" t="s">
-        <v>200</v>
-      </c>
-      <c r="B117" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2">
-      <c r="A118" t="s">
-        <v>202</v>
-      </c>
-      <c r="B118" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2">
-      <c r="A119" t="s">
-        <v>204</v>
-      </c>
-      <c r="B119" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2">
-      <c r="A120" t="s">
-        <v>206</v>
-      </c>
-      <c r="B120" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2">
-      <c r="A121" t="s">
-        <v>208</v>
-      </c>
-      <c r="B121" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2">
-      <c r="A122" t="s">
-        <v>210</v>
-      </c>
-      <c r="B122" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2">
-      <c r="A123" t="s">
-        <v>212</v>
-      </c>
-      <c r="B123" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2">
-      <c r="A124" t="s">
-        <v>213</v>
-      </c>
-      <c r="B124" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="125" spans="1:2">
-      <c r="A125" t="s">
-        <v>214</v>
-      </c>
-      <c r="B125" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="126" spans="1:2">
-      <c r="A126" t="s">
-        <v>215</v>
-      </c>
-      <c r="B126" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="127" spans="1:2">
-      <c r="A127" t="s">
-        <v>217</v>
-      </c>
-      <c r="B127" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="128" spans="1:2">
-      <c r="A128" t="s">
-        <v>219</v>
-      </c>
-      <c r="B128" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="129" spans="1:2">
-      <c r="A129" t="s">
-        <v>221</v>
-      </c>
-      <c r="B129" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="130" spans="1:2">
-      <c r="A130" t="s">
-        <v>223</v>
-      </c>
-      <c r="B130" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="131" spans="1:2">
-      <c r="A131" t="s">
-        <v>176</v>
-      </c>
-      <c r="B131" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="132" spans="1:2">
-      <c r="A132" t="s">
-        <v>177</v>
-      </c>
-      <c r="B132" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="133" spans="1:2">
-      <c r="A133" t="s">
-        <v>179</v>
-      </c>
-      <c r="B133" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="134" spans="1:2">
-      <c r="A134" t="s">
-        <v>178</v>
-      </c>
-      <c r="B134" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="135" spans="1:2">
-      <c r="A135" t="s">
-        <v>229</v>
-      </c>
-      <c r="B135" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="136" spans="1:2">
-      <c r="A136" t="s">
-        <v>230</v>
-      </c>
-      <c r="B136" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="137" spans="1:2">
-      <c r="A137" t="s">
-        <v>232</v>
-      </c>
-      <c r="B137" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="138" spans="1:2">
-      <c r="A138" t="s">
-        <v>234</v>
-      </c>
-      <c r="B138" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="139" spans="1:2">
-      <c r="A139" t="s">
-        <v>236</v>
-      </c>
-      <c r="B139" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="140" spans="1:2">
-      <c r="A140" t="s">
-        <v>238</v>
-      </c>
-      <c r="B140" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="141" spans="1:2">
-      <c r="A141" t="s">
-        <v>240</v>
-      </c>
-      <c r="B141" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="142" spans="1:2">
-      <c r="A142" t="s">
-        <v>241</v>
-      </c>
-      <c r="B142" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="143" spans="1:2">
-      <c r="A143" t="s">
-        <v>242</v>
-      </c>
-      <c r="B143" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="144" spans="1:2">
-      <c r="A144" t="s">
-        <v>243</v>
-      </c>
-      <c r="B144" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2">
-      <c r="A145" t="s">
-        <v>244</v>
-      </c>
-      <c r="B145" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2">
-      <c r="A146" t="s">
-        <v>245</v>
-      </c>
-      <c r="B146" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2">
-      <c r="A147" t="s">
-        <v>246</v>
-      </c>
-      <c r="B147" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2">
-      <c r="A148" t="s">
-        <v>247</v>
-      </c>
-      <c r="B148" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2">
-      <c r="A149" t="s">
-        <v>248</v>
-      </c>
-      <c r="B149" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2">
-      <c r="A150" t="s">
-        <v>250</v>
-      </c>
-      <c r="B150" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2">
-      <c r="A151" t="s">
-        <v>252</v>
-      </c>
-      <c r="B151" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2">
-      <c r="A152" t="s">
-        <v>254</v>
-      </c>
-      <c r="B152" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2">
-      <c r="A153" t="s">
-        <v>256</v>
-      </c>
-      <c r="B153" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2">
-      <c r="A154" t="s">
-        <v>258</v>
-      </c>
-      <c r="B154" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2">
-      <c r="A155" t="s">
-        <v>260</v>
-      </c>
-      <c r="B155" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2">
-      <c r="A156" t="s">
-        <v>262</v>
-      </c>
-      <c r="B156" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2">
-      <c r="A157" t="s">
-        <v>264</v>
-      </c>
-      <c r="B157" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2">
-      <c r="A158" t="s">
-        <v>266</v>
-      </c>
-      <c r="B158" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2">
-      <c r="A159" t="s">
-        <v>268</v>
-      </c>
-      <c r="B159" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2">
-      <c r="A160" t="s">
-        <v>270</v>
-      </c>
-      <c r="B160" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2">
-      <c r="A161" t="s">
-        <v>272</v>
-      </c>
-      <c r="B161" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2">
-      <c r="A162" t="s">
-        <v>274</v>
-      </c>
-      <c r="B162" t="s">
-        <v>275</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2">
-      <c r="A163" t="s">
-        <v>276</v>
-      </c>
-      <c r="B163" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2">
-      <c r="A164" t="s">
-        <v>278</v>
-      </c>
-      <c r="B164" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2">
-      <c r="A165" t="s">
-        <v>280</v>
-      </c>
-      <c r="B165" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2">
-      <c r="A166" t="s">
-        <v>282</v>
-      </c>
-      <c r="B166" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2">
-      <c r="A167" t="s">
-        <v>283</v>
-      </c>
-      <c r="B167" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2">
-      <c r="A168" t="s">
-        <v>284</v>
-      </c>
-      <c r="B168" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2">
-      <c r="A169" t="s">
-        <v>285</v>
-      </c>
-      <c r="B169" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2">
-      <c r="A170" t="s">
-        <v>287</v>
-      </c>
-      <c r="B170" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2">
-      <c r="A171" t="s">
-        <v>289</v>
-      </c>
-      <c r="B171" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2">
-      <c r="A172" t="s">
-        <v>291</v>
-      </c>
-      <c r="B172" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2">
-      <c r="A173" t="s">
-        <v>293</v>
-      </c>
-      <c r="B173" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2">
-      <c r="A174" t="s">
-        <v>295</v>
-      </c>
-      <c r="B174" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2">
-      <c r="A175" t="s">
-        <v>296</v>
-      </c>
-      <c r="B175" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2">
-      <c r="A176" t="s">
-        <v>297</v>
-      </c>
-      <c r="B176" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="177" spans="1:2">
-      <c r="A177" t="s">
-        <v>298</v>
-      </c>
-      <c r="B177" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="178" spans="1:2">
-      <c r="A178" t="s">
-        <v>299</v>
-      </c>
-      <c r="B178" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="179" spans="1:2">
-      <c r="A179" t="s">
-        <v>300</v>
-      </c>
-      <c r="B179" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="180" spans="1:2">
-      <c r="A180" t="s">
-        <v>302</v>
-      </c>
-      <c r="B180" t="s">
-        <v>237</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>
@@ -3210,76 +3285,12 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>310</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>311</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
-      <c r="A6" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="B7" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
   </sheetData>
@@ -3289,12 +3300,31 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>316</v>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
@@ -3304,46 +3334,12 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>306</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>318</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -3353,114 +3349,114 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="1" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B6" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B7" t="s">
-        <v>186</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B8" t="s">
-        <v>120</v>
+        <v>314</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B9" t="s">
-        <v>120</v>
+        <v>314</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B10" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B12" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B13" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B14" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B15" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B16" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B17" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -3530,7 +3526,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
@@ -3546,6 +3542,31 @@
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3555,22 +3576,37 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3580,22 +3616,17 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
         <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3605,17 +3636,22 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>1</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -3630,7 +3666,7 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:1">
